--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Auto Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Auto Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="71">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Auto Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -115,19 +115,31 @@
     <t>Auto Components</t>
   </si>
   <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
     <t>Bharat Forge Ltd.</t>
   </si>
   <si>
     <t>INE465A01025</t>
   </si>
   <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+    <t>Tube Investments of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE974X01010</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
   </si>
   <si>
     <t>Bosch Ltd.</t>
@@ -136,12 +148,6 @@
     <t>INE323A01026</t>
   </si>
   <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
     <t>Balkrishna Industries Ltd.</t>
   </si>
   <si>
@@ -154,12 +160,6 @@
     <t>INE302A01020</t>
   </si>
   <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -217,7 +217,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Auto TRI</t>
   </si>
 </sst>
 </file>
@@ -997,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J79"/>
+  <dimension ref="B1:J78"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1097,10 +1094,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>13521.23</v>
+        <v>14705.629999999997</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9994788386333999</v>
+        <v>0.9999380824189001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1134,10 +1131,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>13521.23</v>
+        <v>14705.629999999997</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9994788386333999</v>
+        <v>0.9999380824189001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1160,13 +1157,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>112251</v>
+        <v>118166</v>
       </c>
       <c r="G8" s="15">
-        <v>3356.14</v>
+        <v>3517.57</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2480832667955</v>
+        <v>0.2391840540375</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1189,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>16682</v>
+        <v>17501</v>
       </c>
       <c r="G9" s="15">
-        <v>2053.66</v>
+        <v>2155.95</v>
       </c>
       <c r="H9" s="16">
-        <v>0.151804955004</v>
+        <v>0.1465980382202</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1218,13 +1215,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>265772</v>
+        <v>278290</v>
       </c>
       <c r="G10" s="15">
-        <v>1903.19</v>
+        <v>2002.30</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1406823292629</v>
+        <v>0.1361503058644</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1247,13 +1244,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>14068</v>
+        <v>14788</v>
       </c>
       <c r="G11" s="15">
-        <v>1244.71</v>
+        <v>1272.80</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0920079981803</v>
+        <v>0.086546526147</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1276,13 +1273,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>17444</v>
+        <v>18323</v>
       </c>
       <c r="G12" s="15">
-        <v>906.09</v>
+        <v>977.26</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0669774703113</v>
+        <v>0.066450705643</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1305,13 +1302,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>29733</v>
+        <v>31316</v>
       </c>
       <c r="G13" s="15">
-        <v>730.81</v>
+        <v>870.84</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0540209086053</v>
+        <v>0.0592144695395</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1334,13 +1331,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>16434</v>
+        <v>17307</v>
       </c>
       <c r="G14" s="15">
-        <v>713.10</v>
+        <v>745.81</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0527117991358</v>
+        <v>0.0507128100767</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1363,13 +1360,13 @@
         <v>32</v>
       </c>
       <c r="F15" s="14">
-        <v>373733</v>
+        <v>393167</v>
       </c>
       <c r="G15" s="15">
-        <v>527.94</v>
+        <v>602.02</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0390249154898</v>
+        <v>0.0409355277113</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1389,16 +1386,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F16" s="14">
-        <v>33143</v>
+        <v>190734</v>
       </c>
       <c r="G16" s="15">
-        <v>405.69</v>
+        <v>450.19</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0299882902698</v>
+        <v>0.0306115498162</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1409,25 +1406,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F17" s="14">
-        <v>181366</v>
+        <v>35556</v>
       </c>
       <c r="G17" s="15">
-        <v>393.26</v>
+        <v>441.21</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0290694743067</v>
+        <v>0.0300009371474</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1450,13 +1447,13 @@
         <v>32</v>
       </c>
       <c r="F18" s="14">
-        <v>1096</v>
+        <v>14339</v>
       </c>
       <c r="G18" s="15">
-        <v>314.87</v>
+        <v>439.07</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0232749462823</v>
+        <v>0.0298554236607</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1479,13 +1476,13 @@
         <v>32</v>
       </c>
       <c r="F19" s="14">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G19" s="15">
-        <v>289.76</v>
+        <v>369.38</v>
       </c>
       <c r="H19" s="16">
-        <v>0.02141883455</v>
+        <v>0.0251167157669</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1508,13 +1505,13 @@
         <v>32</v>
       </c>
       <c r="F20" s="14">
-        <v>10174</v>
+        <v>1154</v>
       </c>
       <c r="G20" s="15">
-        <v>281.95</v>
+        <v>362.53</v>
       </c>
       <c r="H20" s="16">
-        <v>0.020841525405</v>
+        <v>0.0246509366154</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1537,13 +1534,13 @@
         <v>32</v>
       </c>
       <c r="F21" s="14">
-        <v>57620</v>
+        <v>10677</v>
       </c>
       <c r="G21" s="15">
-        <v>215.79</v>
+        <v>263.96</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0159510294987</v>
+        <v>0.0179484766198</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1566,13 +1563,13 @@
         <v>32</v>
       </c>
       <c r="F22" s="14">
-        <v>42137</v>
+        <v>60681</v>
       </c>
       <c r="G22" s="15">
-        <v>184.27</v>
+        <v>234.74</v>
       </c>
       <c r="H22" s="16">
-        <v>0.013621095536</v>
+        <v>0.0159616055529</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2087,10 +2084,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="9">
-        <v>41.86</v>
+        <v>38.50</v>
       </c>
       <c r="H50" s="10">
-        <v>0.003094258746</v>
+        <v>0.0026178828226</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>13</v>
@@ -2124,10 +2121,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="18">
-        <v>-34.8095829000049</v>
+        <v>-37.58940658999927</v>
       </c>
       <c r="H52" s="19">
-        <v>-0.002573097380211378</v>
+        <v>-0.002555965242216316</v>
       </c>
       <c r="I52" s="18" t="s">
         <v>13</v>
@@ -2153,10 +2150,10 @@
         <v>13</v>
       </c>
       <c r="G53" s="18">
-        <v>13528.2804171</v>
+        <v>14706.54059341</v>
       </c>
       <c r="H53" s="19">
-        <v>0.9999999999991886</v>
+        <v>0.9999999999992838</v>
       </c>
       <c r="I53" s="18" t="s">
         <v>13</v>
@@ -2229,11 +2226,6 @@
     <row r="78" ht="15">
       <c r="B78" s="21" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="79" ht="15">
-      <c r="B79" s="21" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
